--- a/survey_templates/025_tv_series_release_viewer_feedback_form--survey_templates.xlsx
+++ b/survey_templates/025_tv_series_release_viewer_feedback_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
